--- a/output/pdf_financials_xlsx/IZO.xlsx
+++ b/output/pdf_financials_xlsx/IZO.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.665674</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.163342</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.163154</v>
       </c>
     </row>
     <row r="93">
@@ -3018,7 +3018,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>1.665674</v>
       </c>

--- a/output/pdf_financials_xlsx/IZO.xlsx
+++ b/output/pdf_financials_xlsx/IZO.xlsx
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>1.145942</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.791957</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>2.446709</v>
       </c>
     </row>
     <row r="65">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.149006</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="68">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.027855</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.013406</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007186</v>
       </c>
     </row>
     <row r="102">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.893439</v>
+        <v>0.9212939999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.199919</v>
+        <v>0.213325</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.675225</v>
+        <v>0.668039</v>
       </c>
     </row>
     <row r="107">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.047457</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.011111</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -3568,7 +3568,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.027855</v>
       </c>
@@ -4209,7 +4213,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.047457</v>
       </c>
